--- a/artfynd/A 15857-2024 artfynd.xlsx
+++ b/artfynd/A 15857-2024 artfynd.xlsx
@@ -6086,11 +6086,11 @@
         <v>119088329</v>
       </c>
       <c r="B55" t="n">
-        <v>56520</v>
+        <v>56593</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7519,11 +7519,11 @@
         <v>119088330</v>
       </c>
       <c r="B69" t="n">
-        <v>56520</v>
+        <v>56593</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">

--- a/artfynd/A 15857-2024 artfynd.xlsx
+++ b/artfynd/A 15857-2024 artfynd.xlsx
@@ -6086,11 +6086,11 @@
         <v>119088329</v>
       </c>
       <c r="B55" t="n">
-        <v>56593</v>
+        <v>56520</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7519,11 +7519,11 @@
         <v>119088330</v>
       </c>
       <c r="B69" t="n">
-        <v>56593</v>
+        <v>56520</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
